--- a/docs/ESP32 Pins.xlsx
+++ b/docs/ESP32 Pins.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dropbox\PlatformIO\Projects\hx3_esp32\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dropbox\PlatformIO\Projects\HX3-WiFi-MenuPanel\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="202">
   <si>
     <t>OK</t>
   </si>
@@ -437,9 +437,6 @@
     <t>pull up</t>
   </si>
   <si>
-    <t>LED</t>
-  </si>
-  <si>
     <t>to pin</t>
   </si>
   <si>
@@ -564,13 +561,82 @@
   </si>
   <si>
     <t>5V IN</t>
+  </si>
+  <si>
+    <t>ER-TFT2.79-1</t>
+  </si>
+  <si>
+    <t>ER 1</t>
+  </si>
+  <si>
+    <t>ER 2</t>
+  </si>
+  <si>
+    <t>ER 5</t>
+  </si>
+  <si>
+    <t>ER 3</t>
+  </si>
+  <si>
+    <t>ER 4</t>
+  </si>
+  <si>
+    <t>ER 7</t>
+  </si>
+  <si>
+    <t>LCD_MISO*</t>
+  </si>
+  <si>
+    <t>BTN ENTER</t>
+  </si>
+  <si>
+    <t>BTN UP</t>
+  </si>
+  <si>
+    <t>BTN DOWN</t>
+  </si>
+  <si>
+    <t>LCD_SCK</t>
+  </si>
+  <si>
+    <t>ER 8, ER10</t>
+  </si>
+  <si>
+    <t>VCC 3V3</t>
+  </si>
+  <si>
+    <t>SCK</t>
+  </si>
+  <si>
+    <t>SI</t>
+  </si>
+  <si>
+    <t>DC</t>
+  </si>
+  <si>
+    <t>CS</t>
+  </si>
+  <si>
+    <t>TE</t>
+  </si>
+  <si>
+    <t>LED K-</t>
+  </si>
+  <si>
+    <t>LED A+</t>
+  </si>
+  <si>
+    <t>GMT20, ER-TFT2.0</t>
+  </si>
+  <si>
+    <t>BL (nur ER)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -657,6 +723,22 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF0070C0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1" tint="0.499984740745262"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -766,7 +848,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -1033,12 +1115,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="107">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1220,9 +1317,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1241,9 +1335,6 @@
     <xf numFmtId="0" fontId="7" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1253,9 +1344,6 @@
     <xf numFmtId="0" fontId="7" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1283,9 +1371,6 @@
     <xf numFmtId="0" fontId="0" fillId="16" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -1357,6 +1442,36 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1367,10 +1482,10 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFF7D7D"/>
       <color rgb="FFF7AFDD"/>
       <color rgb="FFFBD5ED"/>
       <color rgb="FFFFA3A3"/>
-      <color rgb="FFFF7D7D"/>
       <color rgb="FFD3C5DD"/>
     </mruColors>
   </colors>
@@ -1739,7 +1854,7 @@
         <v>12</v>
       </c>
       <c r="I2" s="54" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J2" s="54"/>
       <c r="K2" s="54"/>
@@ -1748,7 +1863,7 @@
       <c r="N2" s="54"/>
       <c r="O2" s="54"/>
       <c r="P2" s="54" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q2" s="54"/>
       <c r="R2" s="54"/>
@@ -1787,7 +1902,7 @@
         <v>2</v>
       </c>
       <c r="H4" s="42" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I4" s="47" t="s">
         <v>9</v>
@@ -1796,10 +1911,10 @@
         <v>9</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O4" s="42" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="P4" s="47" t="s">
         <v>9</v>
@@ -1810,7 +1925,7 @@
         <v>9</v>
       </c>
       <c r="U4" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
@@ -1830,11 +1945,13 @@
       </c>
       <c r="H5" s="42"/>
       <c r="I5" s="56" t="s">
-        <v>162</v>
-      </c>
-      <c r="J5" s="61"/>
-      <c r="K5" s="62"/>
-      <c r="L5" s="90" t="s">
+        <v>161</v>
+      </c>
+      <c r="J5" s="107" t="s">
+        <v>188</v>
+      </c>
+      <c r="K5" s="61"/>
+      <c r="L5" s="86" t="s">
         <v>134</v>
       </c>
       <c r="M5" s="58" t="s">
@@ -1843,13 +1960,16 @@
       <c r="P5" s="55" t="s">
         <v>115</v>
       </c>
-      <c r="Q5" s="76"/>
-      <c r="R5" s="62"/>
-      <c r="S5" s="77" t="s">
-        <v>166</v>
+      <c r="Q5" s="73"/>
+      <c r="R5" s="61"/>
+      <c r="S5" s="74" t="s">
+        <v>165</v>
       </c>
       <c r="T5" s="58" t="s">
         <v>106</v>
+      </c>
+      <c r="U5" s="1" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
@@ -1868,27 +1988,29 @@
         <v>4</v>
       </c>
       <c r="H6" s="42" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I6" s="56" t="s">
-        <v>163</v>
-      </c>
-      <c r="J6" s="63" t="s">
+        <v>162</v>
+      </c>
+      <c r="J6" s="62" t="s">
         <v>74</v>
       </c>
       <c r="K6" s="43"/>
-      <c r="L6" s="91" t="s">
+      <c r="L6" s="87" t="s">
         <v>135</v>
       </c>
       <c r="M6" s="58" t="s">
         <v>117</v>
       </c>
       <c r="P6" s="56" t="s">
-        <v>162</v>
-      </c>
-      <c r="Q6" s="78"/>
+        <v>161</v>
+      </c>
+      <c r="Q6" s="62" t="s">
+        <v>188</v>
+      </c>
       <c r="R6" s="43"/>
-      <c r="S6" s="79" t="s">
+      <c r="S6" s="76" t="s">
         <v>14</v>
       </c>
       <c r="T6" s="58" t="s">
@@ -1913,27 +2035,29 @@
       </c>
       <c r="F7" s="8"/>
       <c r="H7" s="42" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I7" s="56" t="s">
-        <v>164</v>
-      </c>
-      <c r="J7" s="63" t="s">
+        <v>163</v>
+      </c>
+      <c r="J7" s="62" t="s">
         <v>57</v>
       </c>
       <c r="K7" s="43"/>
-      <c r="L7" s="64"/>
+      <c r="L7" s="110" t="s">
+        <v>189</v>
+      </c>
       <c r="M7" s="58" t="s">
         <v>118</v>
       </c>
       <c r="P7" s="56" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q7" s="63" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q7" s="62" t="s">
         <v>74</v>
       </c>
       <c r="R7" s="43"/>
-      <c r="S7" s="91" t="s">
+      <c r="S7" s="87" t="s">
         <v>135</v>
       </c>
       <c r="T7" s="58" t="s">
@@ -1961,22 +2085,24 @@
       </c>
       <c r="H8" s="42"/>
       <c r="I8" s="56" t="s">
-        <v>165</v>
-      </c>
-      <c r="J8" s="65"/>
+        <v>164</v>
+      </c>
+      <c r="J8" s="62" t="s">
+        <v>187</v>
+      </c>
       <c r="K8" s="43"/>
-      <c r="L8" s="64"/>
+      <c r="L8" s="63"/>
       <c r="M8" s="58" t="s">
         <v>119</v>
       </c>
       <c r="P8" s="56" t="s">
-        <v>164</v>
-      </c>
-      <c r="Q8" s="63" t="s">
+        <v>163</v>
+      </c>
+      <c r="Q8" s="62" t="s">
         <v>57</v>
       </c>
       <c r="R8" s="43"/>
-      <c r="S8" s="91" t="s">
+      <c r="S8" s="87" t="s">
         <v>134</v>
       </c>
       <c r="T8" s="58" t="s">
@@ -2002,18 +2128,24 @@
       <c r="I9" s="56" t="s">
         <v>104</v>
       </c>
-      <c r="J9" s="65"/>
+      <c r="J9" s="108" t="s">
+        <v>167</v>
+      </c>
       <c r="K9" s="43"/>
-      <c r="L9" s="64"/>
+      <c r="L9" s="106" t="s">
+        <v>169</v>
+      </c>
       <c r="M9" s="58" t="s">
         <v>120</v>
       </c>
       <c r="P9" s="56" t="s">
-        <v>165</v>
-      </c>
-      <c r="Q9" s="78"/>
+        <v>164</v>
+      </c>
+      <c r="Q9" s="62" t="s">
+        <v>187</v>
+      </c>
       <c r="R9" s="43"/>
-      <c r="S9" s="79" t="s">
+      <c r="S9" s="76" t="s">
         <v>13</v>
       </c>
       <c r="T9" s="58" t="s">
@@ -2039,22 +2171,26 @@
       <c r="I10" s="60" t="s">
         <v>102</v>
       </c>
-      <c r="J10" s="65"/>
+      <c r="J10" s="64"/>
       <c r="K10" s="59" t="s">
-        <v>149</v>
-      </c>
-      <c r="L10" s="64"/>
+        <v>148</v>
+      </c>
+      <c r="L10" s="109" t="s">
+        <v>6</v>
+      </c>
       <c r="M10" s="58" t="s">
         <v>121</v>
       </c>
       <c r="P10" s="56" t="s">
-        <v>160</v>
-      </c>
-      <c r="Q10" s="80" t="s">
-        <v>171</v>
+        <v>159</v>
+      </c>
+      <c r="Q10" s="77" t="s">
+        <v>170</v>
       </c>
       <c r="R10" s="43"/>
-      <c r="S10" s="64"/>
+      <c r="S10" s="78" t="s">
+        <v>186</v>
+      </c>
       <c r="T10" s="58" t="s">
         <v>107</v>
       </c>
@@ -2078,24 +2214,31 @@
       <c r="I11" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="J11" s="65"/>
+      <c r="J11" s="64"/>
       <c r="K11" s="43"/>
-      <c r="L11" s="64"/>
+      <c r="L11" s="109" t="s">
+        <v>6</v>
+      </c>
       <c r="M11" s="58" t="s">
         <v>122</v>
       </c>
       <c r="P11" s="56" t="s">
-        <v>161</v>
-      </c>
-      <c r="Q11" s="78"/>
+        <v>160</v>
+      </c>
+      <c r="Q11" s="103" t="s">
+        <v>189</v>
+      </c>
       <c r="R11" s="59" t="s">
-        <v>176</v>
-      </c>
-      <c r="S11" s="81" t="s">
-        <v>167</v>
+        <v>175</v>
+      </c>
+      <c r="S11" s="78" t="s">
+        <v>166</v>
       </c>
       <c r="T11" s="58" t="s">
         <v>105</v>
+      </c>
+      <c r="U11" s="1" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
@@ -2117,29 +2260,34 @@
       <c r="I12" s="56" t="s">
         <v>105</v>
       </c>
-      <c r="J12" s="65"/>
+      <c r="J12" s="108" t="s">
+        <v>190</v>
+      </c>
       <c r="K12" s="43"/>
-      <c r="L12" s="66" t="s">
+      <c r="L12" s="65" t="s">
         <v>64</v>
       </c>
       <c r="M12" s="58" t="s">
         <v>123</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P12" s="56" t="s">
         <v>118</v>
       </c>
-      <c r="Q12" s="78"/>
+      <c r="Q12" s="75"/>
       <c r="R12" s="59" t="s">
-        <v>177</v>
-      </c>
-      <c r="S12" s="67" t="s">
+        <v>176</v>
+      </c>
+      <c r="S12" s="66" t="s">
         <v>63</v>
       </c>
       <c r="T12" s="58" t="s">
         <v>124</v>
+      </c>
+      <c r="U12" s="1" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
@@ -2161,27 +2309,32 @@
       <c r="I13" s="56" t="s">
         <v>106</v>
       </c>
-      <c r="J13" s="65"/>
+      <c r="J13" s="108" t="s">
+        <v>165</v>
+      </c>
       <c r="K13" s="43"/>
-      <c r="L13" s="67" t="s">
+      <c r="L13" s="66" t="s">
         <v>63</v>
       </c>
       <c r="M13" s="58" t="s">
         <v>124</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P13" s="56" t="s">
         <v>119</v>
       </c>
-      <c r="Q13" s="78"/>
+      <c r="Q13" s="75"/>
       <c r="R13" s="43"/>
-      <c r="S13" s="67" t="s">
+      <c r="S13" s="104" t="s">
         <v>62</v>
       </c>
       <c r="T13" s="58" t="s">
         <v>114</v>
+      </c>
+      <c r="U13" s="1" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
@@ -2203,10 +2356,12 @@
       <c r="I14" s="56" t="s">
         <v>107</v>
       </c>
-      <c r="J14" s="65"/>
+      <c r="J14" s="108" t="s">
+        <v>186</v>
+      </c>
       <c r="K14" s="43"/>
-      <c r="L14" s="68" t="s">
-        <v>137</v>
+      <c r="L14" s="78" t="s">
+        <v>168</v>
       </c>
       <c r="M14" s="58" t="s">
         <v>125</v>
@@ -2214,13 +2369,16 @@
       <c r="P14" s="56" t="s">
         <v>120</v>
       </c>
-      <c r="Q14" s="78"/>
+      <c r="Q14" s="75"/>
       <c r="R14" s="43"/>
-      <c r="S14" s="82" t="s">
+      <c r="S14" s="66" t="s">
         <v>65</v>
       </c>
       <c r="T14" s="58" t="s">
         <v>113</v>
+      </c>
+      <c r="U14" s="1" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
@@ -2239,31 +2397,39 @@
         <v>20</v>
       </c>
       <c r="H15" s="42" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I15" s="56" t="s">
         <v>108</v>
       </c>
-      <c r="J15" s="69" t="s">
+      <c r="J15" s="67" t="s">
         <v>13</v>
       </c>
       <c r="K15" s="43"/>
-      <c r="L15" s="64"/>
+      <c r="L15" s="109" t="s">
+        <v>6</v>
+      </c>
       <c r="M15" s="58" t="s">
         <v>126</v>
       </c>
+      <c r="O15" s="42" t="s">
+        <v>139</v>
+      </c>
       <c r="P15" s="56" t="s">
         <v>110</v>
       </c>
-      <c r="Q15" s="83" t="s">
+      <c r="Q15" s="79" t="s">
         <v>66</v>
       </c>
       <c r="R15" s="43"/>
-      <c r="S15" s="81" t="s">
-        <v>170</v>
+      <c r="S15" s="106" t="s">
+        <v>169</v>
       </c>
       <c r="T15" s="58" t="s">
         <v>112</v>
+      </c>
+      <c r="U15" s="1" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
@@ -2286,29 +2452,34 @@
         <v>19</v>
       </c>
       <c r="H16" s="42" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I16" s="56" t="s">
         <v>109</v>
       </c>
-      <c r="J16" s="69" t="s">
+      <c r="J16" s="67" t="s">
         <v>14</v>
       </c>
       <c r="K16" s="43"/>
-      <c r="L16" s="64"/>
+      <c r="L16" s="109" t="s">
+        <v>6</v>
+      </c>
       <c r="M16" s="58" t="s">
         <v>127</v>
       </c>
       <c r="P16" s="56" t="s">
         <v>111</v>
       </c>
-      <c r="Q16" s="78"/>
+      <c r="Q16" s="75"/>
       <c r="R16" s="43"/>
-      <c r="S16" s="81" t="s">
-        <v>169</v>
+      <c r="S16" s="78" t="s">
+        <v>168</v>
       </c>
       <c r="T16" s="58" t="s">
         <v>125</v>
+      </c>
+      <c r="U16" s="1" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
@@ -2331,31 +2502,39 @@
         <v>21</v>
       </c>
       <c r="H17" s="42" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I17" s="56" t="s">
         <v>110</v>
       </c>
-      <c r="J17" s="70" t="s">
+      <c r="J17" s="68" t="s">
         <v>66</v>
       </c>
       <c r="K17" s="43"/>
-      <c r="L17" s="64"/>
+      <c r="L17" s="109" t="s">
+        <v>6</v>
+      </c>
       <c r="M17" s="58" t="s">
         <v>128</v>
       </c>
+      <c r="O17" s="42" t="s">
+        <v>144</v>
+      </c>
       <c r="P17" s="56" t="s">
         <v>123</v>
       </c>
-      <c r="Q17" s="83" t="s">
+      <c r="Q17" s="79" t="s">
         <v>64</v>
       </c>
       <c r="R17" s="43"/>
-      <c r="S17" s="81" t="s">
-        <v>168</v>
+      <c r="S17" s="78" t="s">
+        <v>167</v>
       </c>
       <c r="T17" s="58" t="s">
         <v>104</v>
+      </c>
+      <c r="U17" s="1" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
@@ -2381,22 +2560,27 @@
       <c r="I18" s="56" t="s">
         <v>111</v>
       </c>
-      <c r="J18" s="65"/>
+      <c r="J18" s="64"/>
       <c r="K18" s="43"/>
-      <c r="L18" s="64"/>
+      <c r="L18" s="109" t="s">
+        <v>6</v>
+      </c>
       <c r="M18" s="58" t="s">
         <v>129</v>
       </c>
       <c r="P18" s="55" t="s">
         <v>71</v>
       </c>
-      <c r="Q18" s="78"/>
+      <c r="Q18" s="75"/>
       <c r="R18" s="46" t="s">
         <v>133</v>
       </c>
-      <c r="S18" s="84"/>
+      <c r="S18" s="80"/>
       <c r="T18" s="57" t="s">
         <v>71</v>
+      </c>
+      <c r="U18" s="1" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="19" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2419,27 +2603,30 @@
         <v>31</v>
       </c>
       <c r="H19" s="42" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I19" s="56" t="s">
         <v>112</v>
       </c>
-      <c r="J19" s="71" t="s">
+      <c r="J19" s="105" t="s">
         <v>62</v>
       </c>
       <c r="K19" s="43"/>
-      <c r="L19" s="64"/>
+      <c r="L19" s="63"/>
       <c r="M19" s="57" t="s">
         <v>71</v>
       </c>
       <c r="P19" s="55" t="s">
         <v>79</v>
       </c>
-      <c r="Q19" s="85"/>
-      <c r="R19" s="74"/>
-      <c r="S19" s="86"/>
+      <c r="Q19" s="81"/>
+      <c r="R19" s="71"/>
+      <c r="S19" s="82"/>
       <c r="T19" s="57" t="s">
-        <v>132</v>
+        <v>131</v>
+      </c>
+      <c r="U19" s="1" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
@@ -2462,16 +2649,16 @@
         <v>67</v>
       </c>
       <c r="H20" s="42" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I20" s="56" t="s">
         <v>113</v>
       </c>
-      <c r="J20" s="72" t="s">
+      <c r="J20" s="69" t="s">
         <v>65</v>
       </c>
       <c r="K20" s="43"/>
-      <c r="L20" s="64"/>
+      <c r="L20" s="63"/>
       <c r="M20" s="57" t="s">
         <v>130</v>
       </c>
@@ -2499,11 +2686,11 @@
       <c r="I21" s="56" t="s">
         <v>114</v>
       </c>
-      <c r="J21" s="65"/>
+      <c r="J21" s="64"/>
       <c r="K21" s="46" t="s">
         <v>133</v>
       </c>
-      <c r="L21" s="64"/>
+      <c r="L21" s="63"/>
       <c r="M21" s="57" t="s">
         <v>131</v>
       </c>
@@ -2527,14 +2714,11 @@
       <c r="I22" s="55" t="s">
         <v>115</v>
       </c>
-      <c r="J22" s="73"/>
-      <c r="K22" s="74"/>
-      <c r="L22" s="75"/>
+      <c r="J22" s="70"/>
+      <c r="K22" s="71"/>
+      <c r="L22" s="72"/>
       <c r="M22" s="57" t="s">
         <v>132</v>
-      </c>
-      <c r="P22" s="54" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
@@ -2552,8 +2736,11 @@
       <c r="F23" s="15" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="24" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P23" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="38">
         <v>22</v>
       </c>
@@ -2568,17 +2755,20 @@
       <c r="F24" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="O24" s="42" t="s">
-        <v>138</v>
-      </c>
-      <c r="P24" s="47" t="s">
-        <v>9</v>
-      </c>
-      <c r="T24" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="U24" s="1" t="s">
-        <v>138</v>
+      <c r="P24" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="T24" s="3" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
@@ -2600,16 +2790,20 @@
       <c r="F25" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="P25" s="55" t="s">
-        <v>179</v>
-      </c>
-      <c r="Q25" s="76"/>
-      <c r="R25" s="92" t="s">
-        <v>175</v>
-      </c>
-      <c r="S25" s="87"/>
-      <c r="T25" s="57" t="s">
-        <v>131</v>
+      <c r="P25" s="19">
+        <v>1</v>
+      </c>
+      <c r="Q25" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="R25" s="19">
+        <v>17</v>
+      </c>
+      <c r="S25" s="32" t="s">
+        <v>83</v>
+      </c>
+      <c r="T25" s="19" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
@@ -2632,17 +2826,22 @@
       <c r="I26" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="P26" s="55" t="s">
-        <v>71</v>
-      </c>
-      <c r="Q26" s="78"/>
-      <c r="R26" s="93"/>
-      <c r="S26" s="102" t="s">
-        <v>0</v>
-      </c>
-      <c r="T26" s="58" t="s">
-        <v>113</v>
-      </c>
+      <c r="P26" s="17">
+        <v>2</v>
+      </c>
+      <c r="Q26" s="44" t="s">
+        <v>63</v>
+      </c>
+      <c r="R26" s="29">
+        <v>5</v>
+      </c>
+      <c r="S26" s="45" t="s">
+        <v>84</v>
+      </c>
+      <c r="T26" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="U26" s="31"/>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
@@ -2657,18 +2856,20 @@
       <c r="D27" s="8"/>
       <c r="E27" s="17"/>
       <c r="F27" s="8"/>
-      <c r="P27" s="56" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q27" s="103" t="s">
-        <v>0</v>
-      </c>
-      <c r="R27" s="43"/>
-      <c r="S27" s="104" t="s">
-        <v>136</v>
-      </c>
-      <c r="T27" s="58" t="s">
-        <v>103</v>
+      <c r="P27" s="19">
+        <v>3</v>
+      </c>
+      <c r="Q27" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="R27" s="19">
+        <v>13</v>
+      </c>
+      <c r="S27" s="32" t="s">
+        <v>85</v>
+      </c>
+      <c r="T27" s="19" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
@@ -2684,16 +2885,20 @@
       <c r="D28" s="8"/>
       <c r="E28" s="17"/>
       <c r="F28" s="8"/>
-      <c r="P28" s="56" t="s">
-        <v>123</v>
-      </c>
-      <c r="Q28" s="105" t="s">
-        <v>0</v>
-      </c>
-      <c r="R28" s="43"/>
-      <c r="S28" s="88"/>
-      <c r="T28" s="57" t="s">
-        <v>71</v>
+      <c r="P28" s="17">
+        <v>4</v>
+      </c>
+      <c r="Q28" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="R28" s="17">
+        <v>16</v>
+      </c>
+      <c r="S28" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="T28" s="17" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
@@ -2709,16 +2914,20 @@
       <c r="D29" s="8"/>
       <c r="E29" s="17"/>
       <c r="F29" s="8"/>
-      <c r="P29" s="56" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q29" s="105" t="s">
-        <v>0</v>
-      </c>
-      <c r="R29" s="43"/>
-      <c r="S29" s="88"/>
-      <c r="T29" s="57" t="s">
-        <v>178</v>
+      <c r="P29" s="19">
+        <v>5</v>
+      </c>
+      <c r="Q29" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="R29" s="19">
+        <v>14</v>
+      </c>
+      <c r="S29" s="32" t="s">
+        <v>87</v>
+      </c>
+      <c r="T29" s="19" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
@@ -2734,18 +2943,16 @@
       <c r="D30" s="8"/>
       <c r="E30" s="17"/>
       <c r="F30" s="8"/>
-      <c r="P30" s="56" t="s">
-        <v>110</v>
-      </c>
-      <c r="Q30" s="105" t="s">
-        <v>0</v>
-      </c>
-      <c r="R30" s="43"/>
-      <c r="S30" s="97" t="s">
-        <v>134</v>
-      </c>
-      <c r="T30" s="58" t="s">
-        <v>116</v>
+      <c r="P30" s="17">
+        <v>6</v>
+      </c>
+      <c r="Q30" s="29"/>
+      <c r="R30" s="29"/>
+      <c r="S30" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="T30" s="17" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
@@ -2771,21 +2978,19 @@
       <c r="J31" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="P31" s="56" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q31" s="103" t="s">
-        <v>0</v>
-      </c>
-      <c r="R31" s="43"/>
-      <c r="S31" s="97" t="s">
-        <v>135</v>
-      </c>
-      <c r="T31" s="58" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="32" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P31" s="19">
+        <v>7</v>
+      </c>
+      <c r="Q31" s="19"/>
+      <c r="R31" s="19"/>
+      <c r="S31" s="32" t="s">
+        <v>89</v>
+      </c>
+      <c r="T31" s="19" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
         <v>35</v>
       </c>
@@ -2810,19 +3015,19 @@
       <c r="J32" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="P32" s="56" t="s">
-        <v>112</v>
-      </c>
-      <c r="Q32" s="106" t="s">
-        <v>0</v>
-      </c>
-      <c r="R32" s="89"/>
-      <c r="S32" s="98"/>
-      <c r="T32" s="57" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="P32" s="17">
+        <v>8</v>
+      </c>
+      <c r="Q32" s="17"/>
+      <c r="R32" s="17"/>
+      <c r="S32" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="T32" s="17" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
         <v>36</v>
       </c>
@@ -2845,13 +3050,19 @@
       <c r="J33" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="Q33" s="99"/>
-      <c r="R33" s="100" t="s">
-        <v>174</v>
-      </c>
-      <c r="S33" s="101"/>
-    </row>
-    <row r="34" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P33" s="28">
+        <v>9</v>
+      </c>
+      <c r="Q33" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="R33" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="S33" s="36"/>
+      <c r="T33" s="36"/>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
         <v>39</v>
       </c>
@@ -2874,16 +3085,24 @@
       <c r="J34" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="Q34" s="94"/>
-      <c r="R34" s="95"/>
-      <c r="S34" s="96"/>
-    </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="P34" s="29">
+        <v>10</v>
+      </c>
+      <c r="Q34" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="R34" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="S34" s="37"/>
+      <c r="T34" s="37"/>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:20" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>46</v>
       </c>
@@ -2894,13 +3113,23 @@
         <v>48</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="I37" s="54" t="s">
+        <v>172</v>
+      </c>
+      <c r="P37" s="54" t="s">
+        <v>200</v>
+      </c>
+      <c r="Q37" s="54"/>
+      <c r="R37" s="111" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A38" s="19">
         <v>1</v>
       </c>
@@ -2916,8 +3145,17 @@
       <c r="E38" s="19" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="P38" s="19">
+        <v>1</v>
+      </c>
+      <c r="Q38" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="R38" s="35" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="17">
         <v>2</v>
       </c>
@@ -2936,8 +3174,29 @@
       <c r="F39" s="31" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="H39" s="42" t="s">
+        <v>137</v>
+      </c>
+      <c r="I39" s="47" t="s">
+        <v>9</v>
+      </c>
+      <c r="M39" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="N39" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="P39" s="17">
+        <v>2</v>
+      </c>
+      <c r="Q39" s="17" t="s">
+        <v>192</v>
+      </c>
+      <c r="R39" s="34" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A40" s="19">
         <v>3</v>
       </c>
@@ -2953,8 +3212,28 @@
       <c r="E40" s="19" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="I40" s="55" t="s">
+        <v>178</v>
+      </c>
+      <c r="J40" s="73"/>
+      <c r="K40" s="88" t="s">
+        <v>174</v>
+      </c>
+      <c r="L40" s="83"/>
+      <c r="M40" s="57" t="s">
+        <v>131</v>
+      </c>
+      <c r="P40" s="19">
+        <v>3</v>
+      </c>
+      <c r="Q40" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="R40" s="35" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A41" s="17">
         <v>4</v>
       </c>
@@ -2970,8 +3249,28 @@
       <c r="E41" s="17" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="I41" s="55" t="s">
+        <v>71</v>
+      </c>
+      <c r="J41" s="75"/>
+      <c r="K41" s="89"/>
+      <c r="L41" s="98" t="s">
+        <v>0</v>
+      </c>
+      <c r="M41" s="58" t="s">
+        <v>113</v>
+      </c>
+      <c r="P41" s="17">
+        <v>4</v>
+      </c>
+      <c r="Q41" s="17" t="s">
+        <v>194</v>
+      </c>
+      <c r="R41" s="34" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A42" s="19">
         <v>5</v>
       </c>
@@ -2987,8 +3286,30 @@
       <c r="E42" s="19" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="I42" s="56" t="s">
+        <v>111</v>
+      </c>
+      <c r="J42" s="99" t="s">
+        <v>0</v>
+      </c>
+      <c r="K42" s="43"/>
+      <c r="L42" s="100" t="s">
+        <v>136</v>
+      </c>
+      <c r="M42" s="58" t="s">
+        <v>103</v>
+      </c>
+      <c r="P42" s="19">
+        <v>5</v>
+      </c>
+      <c r="Q42" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="R42" s="35" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A43" s="17">
         <v>6</v>
       </c>
@@ -3000,8 +3321,28 @@
       <c r="E43" s="17" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="I43" s="56" t="s">
+        <v>123</v>
+      </c>
+      <c r="J43" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="K43" s="43"/>
+      <c r="L43" s="84"/>
+      <c r="M43" s="57" t="s">
+        <v>71</v>
+      </c>
+      <c r="P43" s="17">
+        <v>6</v>
+      </c>
+      <c r="Q43" s="17" t="s">
+        <v>195</v>
+      </c>
+      <c r="R43" s="34" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A44" s="19">
         <v>7</v>
       </c>
@@ -3013,8 +3354,28 @@
       <c r="E44" s="19" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="I44" s="56" t="s">
+        <v>104</v>
+      </c>
+      <c r="J44" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="K44" s="43"/>
+      <c r="L44" s="84"/>
+      <c r="M44" s="57" t="s">
+        <v>177</v>
+      </c>
+      <c r="P44" s="19">
+        <v>7</v>
+      </c>
+      <c r="Q44" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="R44" s="35" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A45" s="17">
         <v>8</v>
       </c>
@@ -3026,8 +3387,30 @@
       <c r="E45" s="17" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="I45" s="56" t="s">
+        <v>110</v>
+      </c>
+      <c r="J45" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="K45" s="43"/>
+      <c r="L45" s="93" t="s">
+        <v>134</v>
+      </c>
+      <c r="M45" s="58" t="s">
+        <v>116</v>
+      </c>
+      <c r="P45" s="17">
+        <v>8</v>
+      </c>
+      <c r="Q45" s="112" t="s">
+        <v>201</v>
+      </c>
+      <c r="R45" s="34" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A46" s="28">
         <v>9</v>
       </c>
@@ -3039,8 +3422,27 @@
       </c>
       <c r="D46" s="36"/>
       <c r="E46" s="36"/>
-    </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="I46" s="56" t="s">
+        <v>125</v>
+      </c>
+      <c r="J46" s="99" t="s">
+        <v>0</v>
+      </c>
+      <c r="K46" s="43"/>
+      <c r="L46" s="93" t="s">
+        <v>135</v>
+      </c>
+      <c r="M46" s="58" t="s">
+        <v>117</v>
+      </c>
+      <c r="P46" s="28">
+        <v>9</v>
+      </c>
+      <c r="R46" s="35" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="47" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="29">
         <v>10</v>
       </c>
@@ -3052,11 +3454,38 @@
       </c>
       <c r="D47" s="37"/>
       <c r="E47" s="37"/>
-    </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="I47" s="56" t="s">
+        <v>112</v>
+      </c>
+      <c r="J47" s="102" t="s">
+        <v>0</v>
+      </c>
+      <c r="K47" s="85"/>
+      <c r="L47" s="94"/>
+      <c r="M47" s="57" t="s">
+        <v>71</v>
+      </c>
+      <c r="P47" s="29">
+        <v>10</v>
+      </c>
+      <c r="R47" s="34" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="J48" s="95"/>
+      <c r="K48" s="96" t="s">
+        <v>173</v>
+      </c>
+      <c r="L48" s="97"/>
+    </row>
+    <row r="49" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
         <v>81</v>
       </c>
+      <c r="J49" s="90"/>
+      <c r="K49" s="91"/>
+      <c r="L49" s="92"/>
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
@@ -3111,15 +3540,6 @@
         <v>2</v>
       </c>
       <c r="D53" s="39"/>
-      <c r="I53" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="J53" s="48" t="s">
-        <v>156</v>
-      </c>
-      <c r="K53" s="48"/>
-      <c r="Q53" s="48"/>
-      <c r="R53" s="48"/>
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A54" s="17">
@@ -3132,14 +3552,6 @@
         <v>33</v>
       </c>
       <c r="D54" s="40"/>
-      <c r="I54" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="L54" s="49" t="s">
-        <v>155</v>
-      </c>
-      <c r="M54" s="49"/>
-      <c r="N54" s="49"/>
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A55" s="19">
@@ -3154,11 +3566,6 @@
       <c r="D55" s="39">
         <v>21</v>
       </c>
-      <c r="I55" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="M55" s="50"/>
-      <c r="N55" s="50"/>
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A56" s="17">
@@ -3173,13 +3580,6 @@
       <c r="D56" s="40">
         <v>22</v>
       </c>
-      <c r="I56" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="O56" s="51" t="s">
-        <v>157</v>
-      </c>
-      <c r="P56" s="51"/>
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A57" s="19">
@@ -3194,13 +3594,6 @@
       <c r="D57" s="39" t="s">
         <v>71</v>
       </c>
-      <c r="I57" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="O57" s="52" t="s">
-        <v>158</v>
-      </c>
-      <c r="P57" s="52"/>
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A58" s="17">
@@ -3276,8 +3669,17 @@
       <c r="D64" s="32" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="I64" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="J64" s="48" t="s">
+        <v>155</v>
+      </c>
+      <c r="K64" s="48"/>
+      <c r="Q64" s="48"/>
+      <c r="R64" s="48"/>
+    </row>
+    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A65" s="17">
         <v>2</v>
       </c>
@@ -3290,8 +3692,16 @@
       <c r="D65" s="5" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="I65" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="L65" s="49" t="s">
+        <v>154</v>
+      </c>
+      <c r="M65" s="49"/>
+      <c r="N65" s="49"/>
+    </row>
+    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A66" s="19">
         <v>3</v>
       </c>
@@ -3304,8 +3714,13 @@
       <c r="D66" s="32" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="I66" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="M66" s="50"/>
+      <c r="N66" s="50"/>
+    </row>
+    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A67" s="17">
         <v>4</v>
       </c>
@@ -3318,8 +3733,15 @@
       <c r="D67" s="5" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="I67" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="O67" s="51" t="s">
+        <v>156</v>
+      </c>
+      <c r="P67" s="51"/>
+    </row>
+    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A68" s="19">
         <v>5</v>
       </c>
@@ -3332,8 +3754,15 @@
       <c r="D68" s="32" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="I68" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="O68" s="52" t="s">
+        <v>157</v>
+      </c>
+      <c r="P68" s="52"/>
+    </row>
+    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A69" s="17">
         <v>6</v>
       </c>
@@ -3350,7 +3779,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A70" s="19">
         <v>7</v>
       </c>
@@ -3367,7 +3796,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A71" s="17">
         <v>8</v>
       </c>
@@ -3384,7 +3813,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A72" s="28">
         <v>9</v>
       </c>
@@ -3401,7 +3830,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A73" s="29">
         <v>10</v>
       </c>
@@ -3414,14 +3843,14 @@
       <c r="D73" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="F73" s="3"/>
+      <c r="G73" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="I26" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="45" orientation="landscape" r:id="rId2"/>
+  <pageSetup paperSize="9" scale="31" orientation="portrait" r:id="rId2"/>
   <drawing r:id="rId3"/>
 </worksheet>
 </file>
--- a/docs/ESP32 Pins.xlsx
+++ b/docs/ESP32 Pins.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="194">
   <si>
     <t>OK</t>
   </si>
@@ -110,9 +110,6 @@
     <t>on-board LED, must be left floating or LOW to enter flash mode</t>
   </si>
   <si>
-    <t>FPGA Pin</t>
-  </si>
-  <si>
     <t>P128</t>
   </si>
   <si>
@@ -122,30 +119,6 @@
     <t>Umbelegt HSPI MISO</t>
   </si>
   <si>
-    <t>P128 (1)</t>
-  </si>
-  <si>
-    <t>P129 (2)</t>
-  </si>
-  <si>
-    <t>P127 (3)</t>
-  </si>
-  <si>
-    <t>P1 (6)</t>
-  </si>
-  <si>
-    <t>P126 (4)</t>
-  </si>
-  <si>
-    <t>P103 (7)</t>
-  </si>
-  <si>
-    <t>P87 (8)</t>
-  </si>
-  <si>
-    <t>P104 (9)</t>
-  </si>
-  <si>
     <t>outputs PWM signal at boot, must be LOW to enter flash mode</t>
   </si>
   <si>
@@ -161,9 +134,6 @@
     <t>Might disturb at startup</t>
   </si>
   <si>
-    <t>P132 (5)</t>
-  </si>
-  <si>
     <t>Pin</t>
   </si>
   <si>
@@ -209,9 +179,6 @@
     <t>ENA_QSPI</t>
   </si>
   <si>
-    <t>P124 (10)</t>
-  </si>
-  <si>
     <t>ESP_RS</t>
   </si>
   <si>
@@ -233,12 +200,6 @@
     <t>ESP_REQU</t>
   </si>
   <si>
-    <t>P96</t>
-  </si>
-  <si>
-    <t>P94</t>
-  </si>
-  <si>
     <t>GND</t>
   </si>
   <si>
@@ -521,24 +482,6 @@
     <t>I_35</t>
   </si>
   <si>
-    <t>LCD_MOSI</t>
-  </si>
-  <si>
-    <t>LCD_SCLK</t>
-  </si>
-  <si>
-    <t>LCD_CS</t>
-  </si>
-  <si>
-    <t>LCD_DC</t>
-  </si>
-  <si>
-    <t>LCD_RST</t>
-  </si>
-  <si>
-    <t>LCD_BLK</t>
-  </si>
-  <si>
     <t>DevKit 1, IdeaSpark TFT 1.9</t>
   </si>
   <si>
@@ -584,9 +527,6 @@
     <t>ER 7</t>
   </si>
   <si>
-    <t>LCD_MISO*</t>
-  </si>
-  <si>
     <t>BTN ENTER</t>
   </si>
   <si>
@@ -596,9 +536,6 @@
     <t>BTN DOWN</t>
   </si>
   <si>
-    <t>LCD_SCK</t>
-  </si>
-  <si>
     <t>ER 8, ER10</t>
   </si>
   <si>
@@ -630,6 +567,45 @@
   </si>
   <si>
     <t>BL (nur ER)</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>ESP</t>
+  </si>
+  <si>
+    <t>10R 1206</t>
+  </si>
+  <si>
+    <t>TFT_MOSI</t>
+  </si>
+  <si>
+    <t>TFT_CS</t>
+  </si>
+  <si>
+    <t>TFT_RST</t>
+  </si>
+  <si>
+    <t>TFT_BL</t>
+  </si>
+  <si>
+    <t>TFT_MISO*</t>
+  </si>
+  <si>
+    <t>TFT_SCLK</t>
+  </si>
+  <si>
+    <t>TFT_SCK</t>
+  </si>
+  <si>
+    <t>TFT_DC</t>
+  </si>
+  <si>
+    <t>TFT Signal</t>
+  </si>
+  <si>
+    <t>TFT_MISO</t>
   </si>
 </sst>
 </file>
@@ -1135,7 +1111,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="113">
+  <cellXfs count="114">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1200,9 +1176,6 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1471,6 +1444,12 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1830,8 +1809,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="27" t="s">
-        <v>82</v>
+      <c r="A1" s="26" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
@@ -1845,37 +1824,37 @@
         <v>11</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>28</v>
+        <v>192</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="54" t="s">
-        <v>158</v>
-      </c>
-      <c r="J2" s="54"/>
-      <c r="K2" s="54"/>
-      <c r="L2" s="54"/>
-      <c r="M2" s="54"/>
-      <c r="N2" s="54"/>
-      <c r="O2" s="54"/>
-      <c r="P2" s="54" t="s">
-        <v>171</v>
-      </c>
-      <c r="Q2" s="54"/>
-      <c r="R2" s="54"/>
-      <c r="S2" s="54"/>
-      <c r="T2" s="54"/>
+      <c r="I2" s="53" t="s">
+        <v>145</v>
+      </c>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="53"/>
+      <c r="M2" s="53"/>
+      <c r="N2" s="53"/>
+      <c r="O2" s="53"/>
+      <c r="P2" s="53" t="s">
+        <v>152</v>
+      </c>
+      <c r="Q2" s="53"/>
+      <c r="R2" s="53"/>
+      <c r="S2" s="53"/>
+      <c r="T2" s="53"/>
     </row>
     <row r="3" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
         <v>0</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="C3" s="16" t="s">
         <v>0</v>
@@ -1883,7 +1862,7 @@
       <c r="D3" s="8"/>
       <c r="E3" s="5"/>
       <c r="F3" s="8" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1901,31 +1880,31 @@
       <c r="F4" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="H4" s="42" t="s">
-        <v>137</v>
-      </c>
-      <c r="I4" s="47" t="s">
+      <c r="H4" s="41" t="s">
+        <v>124</v>
+      </c>
+      <c r="I4" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="M4" s="37" t="s">
+      <c r="M4" s="36" t="s">
         <v>9</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="O4" s="42" t="s">
-        <v>137</v>
-      </c>
-      <c r="P4" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="O4" s="41" t="s">
+        <v>124</v>
+      </c>
+      <c r="P4" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="Q4" s="53"/>
-      <c r="S4" s="42"/>
-      <c r="T4" s="37" t="s">
+      <c r="Q4" s="52"/>
+      <c r="S4" s="41"/>
+      <c r="T4" s="36" t="s">
         <v>9</v>
       </c>
       <c r="U4" s="1" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
@@ -1938,38 +1917,40 @@
       <c r="C5" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="8"/>
+      <c r="D5" s="8" t="s">
+        <v>191</v>
+      </c>
       <c r="E5" s="5"/>
       <c r="F5" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="H5" s="42"/>
-      <c r="I5" s="56" t="s">
+      <c r="H5" s="41"/>
+      <c r="I5" s="55" t="s">
+        <v>148</v>
+      </c>
+      <c r="J5" s="106" t="s">
+        <v>168</v>
+      </c>
+      <c r="K5" s="60"/>
+      <c r="L5" s="85" t="s">
+        <v>121</v>
+      </c>
+      <c r="M5" s="57" t="s">
+        <v>103</v>
+      </c>
+      <c r="P5" s="54" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q5" s="72"/>
+      <c r="R5" s="60"/>
+      <c r="S5" s="73" t="s">
+        <v>184</v>
+      </c>
+      <c r="T5" s="57" t="s">
+        <v>93</v>
+      </c>
+      <c r="U5" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="J5" s="107" t="s">
-        <v>188</v>
-      </c>
-      <c r="K5" s="61"/>
-      <c r="L5" s="86" t="s">
-        <v>134</v>
-      </c>
-      <c r="M5" s="58" t="s">
-        <v>116</v>
-      </c>
-      <c r="P5" s="55" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q5" s="73"/>
-      <c r="R5" s="61"/>
-      <c r="S5" s="74" t="s">
-        <v>165</v>
-      </c>
-      <c r="T5" s="58" t="s">
-        <v>106</v>
-      </c>
-      <c r="U5" s="1" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
@@ -1987,34 +1968,34 @@
       <c r="F6" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="42" t="s">
-        <v>142</v>
-      </c>
-      <c r="I6" s="56" t="s">
-        <v>162</v>
-      </c>
-      <c r="J6" s="62" t="s">
-        <v>74</v>
-      </c>
-      <c r="K6" s="43"/>
-      <c r="L6" s="87" t="s">
-        <v>135</v>
-      </c>
-      <c r="M6" s="58" t="s">
-        <v>117</v>
-      </c>
-      <c r="P6" s="56" t="s">
-        <v>161</v>
-      </c>
-      <c r="Q6" s="62" t="s">
-        <v>188</v>
-      </c>
-      <c r="R6" s="43"/>
-      <c r="S6" s="76" t="s">
+      <c r="H6" s="41" t="s">
+        <v>129</v>
+      </c>
+      <c r="I6" s="55" t="s">
+        <v>149</v>
+      </c>
+      <c r="J6" s="61" t="s">
+        <v>61</v>
+      </c>
+      <c r="K6" s="42"/>
+      <c r="L6" s="86" t="s">
+        <v>122</v>
+      </c>
+      <c r="M6" s="57" t="s">
+        <v>104</v>
+      </c>
+      <c r="P6" s="55" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q6" s="61" t="s">
+        <v>168</v>
+      </c>
+      <c r="R6" s="42"/>
+      <c r="S6" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="T6" s="58" t="s">
-        <v>109</v>
+      <c r="T6" s="57" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
@@ -2027,41 +2008,39 @@
       <c r="C7" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="D7" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="E7" s="24" t="s">
-        <v>62</v>
+      <c r="D7" s="8"/>
+      <c r="E7" s="23" t="s">
+        <v>51</v>
       </c>
       <c r="F7" s="8"/>
-      <c r="H7" s="42" t="s">
-        <v>140</v>
-      </c>
-      <c r="I7" s="56" t="s">
-        <v>163</v>
-      </c>
-      <c r="J7" s="62" t="s">
-        <v>57</v>
-      </c>
-      <c r="K7" s="43"/>
-      <c r="L7" s="110" t="s">
-        <v>189</v>
-      </c>
-      <c r="M7" s="58" t="s">
-        <v>118</v>
-      </c>
-      <c r="P7" s="56" t="s">
-        <v>162</v>
-      </c>
-      <c r="Q7" s="62" t="s">
-        <v>74</v>
-      </c>
-      <c r="R7" s="43"/>
-      <c r="S7" s="87" t="s">
-        <v>135</v>
-      </c>
-      <c r="T7" s="58" t="s">
-        <v>117</v>
+      <c r="H7" s="41" t="s">
+        <v>127</v>
+      </c>
+      <c r="I7" s="55" t="s">
+        <v>150</v>
+      </c>
+      <c r="J7" s="61" t="s">
+        <v>47</v>
+      </c>
+      <c r="K7" s="42"/>
+      <c r="L7" s="109" t="s">
+        <v>169</v>
+      </c>
+      <c r="M7" s="57" t="s">
+        <v>105</v>
+      </c>
+      <c r="P7" s="55" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q7" s="61" t="s">
+        <v>61</v>
+      </c>
+      <c r="R7" s="42"/>
+      <c r="S7" s="86" t="s">
+        <v>122</v>
+      </c>
+      <c r="T7" s="57" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
@@ -2074,39 +2053,37 @@
       <c r="C8" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="D8" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="E8" s="24" t="s">
-        <v>63</v>
+      <c r="D8" s="8"/>
+      <c r="E8" s="23" t="s">
+        <v>52</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="H8" s="42"/>
-      <c r="I8" s="56" t="s">
-        <v>164</v>
-      </c>
-      <c r="J8" s="62" t="s">
-        <v>187</v>
-      </c>
-      <c r="K8" s="43"/>
-      <c r="L8" s="63"/>
-      <c r="M8" s="58" t="s">
-        <v>119</v>
-      </c>
-      <c r="P8" s="56" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q8" s="62" t="s">
-        <v>57</v>
-      </c>
-      <c r="R8" s="43"/>
-      <c r="S8" s="87" t="s">
-        <v>134</v>
-      </c>
-      <c r="T8" s="58" t="s">
-        <v>116</v>
+      <c r="H8" s="41"/>
+      <c r="I8" s="55" t="s">
+        <v>151</v>
+      </c>
+      <c r="J8" s="61" t="s">
+        <v>167</v>
+      </c>
+      <c r="K8" s="42"/>
+      <c r="L8" s="62"/>
+      <c r="M8" s="57" t="s">
+        <v>106</v>
+      </c>
+      <c r="P8" s="55" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q8" s="61" t="s">
+        <v>47</v>
+      </c>
+      <c r="R8" s="42"/>
+      <c r="S8" s="86" t="s">
+        <v>121</v>
+      </c>
+      <c r="T8" s="57" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
@@ -2124,32 +2101,32 @@
       <c r="F9" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="H9" s="42"/>
-      <c r="I9" s="56" t="s">
-        <v>104</v>
-      </c>
-      <c r="J9" s="108" t="s">
+      <c r="H9" s="41"/>
+      <c r="I9" s="55" t="s">
+        <v>91</v>
+      </c>
+      <c r="J9" s="107" t="s">
+        <v>185</v>
+      </c>
+      <c r="K9" s="42"/>
+      <c r="L9" s="105" t="s">
+        <v>186</v>
+      </c>
+      <c r="M9" s="57" t="s">
+        <v>107</v>
+      </c>
+      <c r="P9" s="55" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q9" s="61" t="s">
         <v>167</v>
       </c>
-      <c r="K9" s="43"/>
-      <c r="L9" s="106" t="s">
-        <v>169</v>
-      </c>
-      <c r="M9" s="58" t="s">
-        <v>120</v>
-      </c>
-      <c r="P9" s="56" t="s">
-        <v>164</v>
-      </c>
-      <c r="Q9" s="62" t="s">
-        <v>187</v>
-      </c>
-      <c r="R9" s="43"/>
-      <c r="S9" s="76" t="s">
+      <c r="R9" s="42"/>
+      <c r="S9" s="75" t="s">
         <v>13</v>
       </c>
-      <c r="T9" s="58" t="s">
-        <v>108</v>
+      <c r="T9" s="57" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
@@ -2167,32 +2144,32 @@
       <c r="F10" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="H10" s="42"/>
-      <c r="I10" s="60" t="s">
-        <v>102</v>
-      </c>
-      <c r="J10" s="64"/>
-      <c r="K10" s="59" t="s">
-        <v>148</v>
-      </c>
-      <c r="L10" s="109" t="s">
+      <c r="H10" s="41"/>
+      <c r="I10" s="59" t="s">
+        <v>89</v>
+      </c>
+      <c r="J10" s="63"/>
+      <c r="K10" s="58" t="s">
+        <v>135</v>
+      </c>
+      <c r="L10" s="108" t="s">
         <v>6</v>
       </c>
-      <c r="M10" s="58" t="s">
-        <v>121</v>
-      </c>
-      <c r="P10" s="56" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q10" s="77" t="s">
-        <v>170</v>
-      </c>
-      <c r="R10" s="43"/>
-      <c r="S10" s="78" t="s">
-        <v>186</v>
-      </c>
-      <c r="T10" s="58" t="s">
-        <v>107</v>
+      <c r="M10" s="57" t="s">
+        <v>108</v>
+      </c>
+      <c r="P10" s="55" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q10" s="76" t="s">
+        <v>187</v>
+      </c>
+      <c r="R10" s="42"/>
+      <c r="S10" s="77" t="s">
+        <v>188</v>
+      </c>
+      <c r="T10" s="57" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
@@ -2210,35 +2187,35 @@
       <c r="F11" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="H11" s="42"/>
-      <c r="I11" s="56" t="s">
-        <v>103</v>
-      </c>
-      <c r="J11" s="64"/>
-      <c r="K11" s="43"/>
-      <c r="L11" s="109" t="s">
+      <c r="H11" s="41"/>
+      <c r="I11" s="55" t="s">
+        <v>90</v>
+      </c>
+      <c r="J11" s="63"/>
+      <c r="K11" s="42"/>
+      <c r="L11" s="108" t="s">
         <v>6</v>
       </c>
-      <c r="M11" s="58" t="s">
-        <v>122</v>
-      </c>
-      <c r="P11" s="56" t="s">
-        <v>160</v>
-      </c>
-      <c r="Q11" s="103" t="s">
+      <c r="M11" s="57" t="s">
+        <v>109</v>
+      </c>
+      <c r="P11" s="55" t="s">
+        <v>147</v>
+      </c>
+      <c r="Q11" s="102" t="s">
+        <v>169</v>
+      </c>
+      <c r="R11" s="58" t="s">
+        <v>156</v>
+      </c>
+      <c r="S11" s="77" t="s">
         <v>189</v>
       </c>
-      <c r="R11" s="59" t="s">
-        <v>175</v>
-      </c>
-      <c r="S11" s="78" t="s">
-        <v>166</v>
-      </c>
-      <c r="T11" s="58" t="s">
-        <v>105</v>
+      <c r="T11" s="57" t="s">
+        <v>92</v>
       </c>
       <c r="U11" s="1" t="s">
-        <v>181</v>
+        <v>162</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
@@ -2256,38 +2233,38 @@
       <c r="F12" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="H12" s="42"/>
-      <c r="I12" s="56" t="s">
+      <c r="H12" s="41"/>
+      <c r="I12" s="55" t="s">
+        <v>92</v>
+      </c>
+      <c r="J12" s="107" t="s">
+        <v>190</v>
+      </c>
+      <c r="K12" s="42"/>
+      <c r="L12" s="64" t="s">
+        <v>53</v>
+      </c>
+      <c r="M12" s="57" t="s">
+        <v>110</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="P12" s="55" t="s">
         <v>105</v>
       </c>
-      <c r="J12" s="108" t="s">
-        <v>190</v>
-      </c>
-      <c r="K12" s="43"/>
-      <c r="L12" s="65" t="s">
-        <v>64</v>
-      </c>
-      <c r="M12" s="58" t="s">
-        <v>123</v>
-      </c>
-      <c r="N12" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="P12" s="56" t="s">
-        <v>118</v>
-      </c>
-      <c r="Q12" s="75"/>
-      <c r="R12" s="59" t="s">
-        <v>176</v>
-      </c>
-      <c r="S12" s="66" t="s">
-        <v>63</v>
-      </c>
-      <c r="T12" s="58" t="s">
-        <v>124</v>
+      <c r="Q12" s="74"/>
+      <c r="R12" s="58" t="s">
+        <v>157</v>
+      </c>
+      <c r="S12" s="65" t="s">
+        <v>52</v>
+      </c>
+      <c r="T12" s="57" t="s">
+        <v>111</v>
       </c>
       <c r="U12" s="1" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
@@ -2305,36 +2282,36 @@
       <c r="F13" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="H13" s="42"/>
-      <c r="I13" s="56" t="s">
+      <c r="H13" s="41"/>
+      <c r="I13" s="55" t="s">
+        <v>93</v>
+      </c>
+      <c r="J13" s="107" t="s">
+        <v>184</v>
+      </c>
+      <c r="K13" s="42"/>
+      <c r="L13" s="65" t="s">
+        <v>52</v>
+      </c>
+      <c r="M13" s="57" t="s">
+        <v>111</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="P13" s="55" t="s">
         <v>106</v>
       </c>
-      <c r="J13" s="108" t="s">
-        <v>165</v>
-      </c>
-      <c r="K13" s="43"/>
-      <c r="L13" s="66" t="s">
-        <v>63</v>
-      </c>
-      <c r="M13" s="58" t="s">
-        <v>124</v>
-      </c>
-      <c r="N13" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="P13" s="56" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q13" s="75"/>
-      <c r="R13" s="43"/>
-      <c r="S13" s="104" t="s">
-        <v>62</v>
-      </c>
-      <c r="T13" s="58" t="s">
-        <v>114</v>
+      <c r="Q13" s="74"/>
+      <c r="R13" s="42"/>
+      <c r="S13" s="103" t="s">
+        <v>51</v>
+      </c>
+      <c r="T13" s="57" t="s">
+        <v>101</v>
       </c>
       <c r="U13" s="1" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
@@ -2352,33 +2329,33 @@
       <c r="F14" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="H14" s="42"/>
-      <c r="I14" s="56" t="s">
+      <c r="H14" s="41"/>
+      <c r="I14" s="55" t="s">
+        <v>94</v>
+      </c>
+      <c r="J14" s="107" t="s">
+        <v>188</v>
+      </c>
+      <c r="K14" s="42"/>
+      <c r="L14" s="77" t="s">
+        <v>191</v>
+      </c>
+      <c r="M14" s="57" t="s">
+        <v>112</v>
+      </c>
+      <c r="P14" s="55" t="s">
         <v>107</v>
       </c>
-      <c r="J14" s="108" t="s">
-        <v>186</v>
-      </c>
-      <c r="K14" s="43"/>
-      <c r="L14" s="78" t="s">
-        <v>168</v>
-      </c>
-      <c r="M14" s="58" t="s">
-        <v>125</v>
-      </c>
-      <c r="P14" s="56" t="s">
-        <v>120</v>
-      </c>
-      <c r="Q14" s="75"/>
-      <c r="R14" s="43"/>
-      <c r="S14" s="66" t="s">
-        <v>65</v>
-      </c>
-      <c r="T14" s="58" t="s">
-        <v>113</v>
+      <c r="Q14" s="74"/>
+      <c r="R14" s="42"/>
+      <c r="S14" s="65" t="s">
+        <v>54</v>
+      </c>
+      <c r="T14" s="57" t="s">
+        <v>100</v>
       </c>
       <c r="U14" s="1" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
@@ -2396,40 +2373,40 @@
       <c r="F15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="H15" s="42" t="s">
-        <v>141</v>
-      </c>
-      <c r="I15" s="56" t="s">
-        <v>108</v>
-      </c>
-      <c r="J15" s="67" t="s">
+      <c r="H15" s="41" t="s">
+        <v>128</v>
+      </c>
+      <c r="I15" s="55" t="s">
+        <v>95</v>
+      </c>
+      <c r="J15" s="66" t="s">
         <v>13</v>
       </c>
-      <c r="K15" s="43"/>
-      <c r="L15" s="109" t="s">
+      <c r="K15" s="42"/>
+      <c r="L15" s="108" t="s">
         <v>6</v>
       </c>
-      <c r="M15" s="58" t="s">
+      <c r="M15" s="57" t="s">
+        <v>113</v>
+      </c>
+      <c r="O15" s="41" t="s">
         <v>126</v>
       </c>
-      <c r="O15" s="42" t="s">
-        <v>139</v>
-      </c>
-      <c r="P15" s="56" t="s">
-        <v>110</v>
-      </c>
-      <c r="Q15" s="79" t="s">
-        <v>66</v>
-      </c>
-      <c r="R15" s="43"/>
-      <c r="S15" s="106" t="s">
-        <v>169</v>
-      </c>
-      <c r="T15" s="58" t="s">
-        <v>112</v>
+      <c r="P15" s="55" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q15" s="78" t="s">
+        <v>55</v>
+      </c>
+      <c r="R15" s="42"/>
+      <c r="S15" s="105" t="s">
+        <v>186</v>
+      </c>
+      <c r="T15" s="57" t="s">
+        <v>99</v>
       </c>
       <c r="U15" s="1" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
@@ -2442,44 +2419,42 @@
       <c r="C16" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="D16" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="E16" s="23" t="s">
-        <v>64</v>
+      <c r="D16" s="8"/>
+      <c r="E16" s="22" t="s">
+        <v>53</v>
       </c>
       <c r="F16" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="H16" s="42" t="s">
-        <v>143</v>
-      </c>
-      <c r="I16" s="56" t="s">
-        <v>109</v>
-      </c>
-      <c r="J16" s="67" t="s">
+      <c r="H16" s="41" t="s">
+        <v>130</v>
+      </c>
+      <c r="I16" s="55" t="s">
+        <v>96</v>
+      </c>
+      <c r="J16" s="66" t="s">
         <v>14</v>
       </c>
-      <c r="K16" s="43"/>
-      <c r="L16" s="109" t="s">
+      <c r="K16" s="42"/>
+      <c r="L16" s="108" t="s">
         <v>6</v>
       </c>
-      <c r="M16" s="58" t="s">
-        <v>127</v>
-      </c>
-      <c r="P16" s="56" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q16" s="75"/>
-      <c r="R16" s="43"/>
-      <c r="S16" s="78" t="s">
-        <v>168</v>
-      </c>
-      <c r="T16" s="58" t="s">
-        <v>125</v>
+      <c r="M16" s="57" t="s">
+        <v>114</v>
+      </c>
+      <c r="P16" s="55" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q16" s="74"/>
+      <c r="R16" s="42"/>
+      <c r="S16" s="77" t="s">
+        <v>191</v>
+      </c>
+      <c r="T16" s="57" t="s">
+        <v>112</v>
       </c>
       <c r="U16" s="1" t="s">
-        <v>183</v>
+        <v>164</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
@@ -2492,49 +2467,47 @@
       <c r="C17" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="D17" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E17" s="23" t="s">
-        <v>66</v>
+      <c r="D17" s="8"/>
+      <c r="E17" s="22" t="s">
+        <v>55</v>
       </c>
       <c r="F17" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="H17" s="42" t="s">
-        <v>139</v>
-      </c>
-      <c r="I17" s="56" t="s">
+      <c r="H17" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="I17" s="55" t="s">
+        <v>97</v>
+      </c>
+      <c r="J17" s="67" t="s">
+        <v>55</v>
+      </c>
+      <c r="K17" s="42"/>
+      <c r="L17" s="108" t="s">
+        <v>6</v>
+      </c>
+      <c r="M17" s="57" t="s">
+        <v>115</v>
+      </c>
+      <c r="O17" s="41" t="s">
+        <v>131</v>
+      </c>
+      <c r="P17" s="55" t="s">
         <v>110</v>
       </c>
-      <c r="J17" s="68" t="s">
-        <v>66</v>
-      </c>
-      <c r="K17" s="43"/>
-      <c r="L17" s="109" t="s">
-        <v>6</v>
-      </c>
-      <c r="M17" s="58" t="s">
-        <v>128</v>
-      </c>
-      <c r="O17" s="42" t="s">
-        <v>144</v>
-      </c>
-      <c r="P17" s="56" t="s">
-        <v>123</v>
-      </c>
-      <c r="Q17" s="79" t="s">
-        <v>64</v>
-      </c>
-      <c r="R17" s="43"/>
-      <c r="S17" s="78" t="s">
-        <v>167</v>
-      </c>
-      <c r="T17" s="58" t="s">
-        <v>104</v>
+      <c r="Q17" s="78" t="s">
+        <v>53</v>
+      </c>
+      <c r="R17" s="42"/>
+      <c r="S17" s="77" t="s">
+        <v>185</v>
+      </c>
+      <c r="T17" s="57" t="s">
+        <v>91</v>
       </c>
       <c r="U17" s="1" t="s">
-        <v>182</v>
+        <v>163</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
@@ -2548,39 +2521,37 @@
         <v>0</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E18" s="22" t="s">
-        <v>25</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="E18" s="113"/>
       <c r="F18" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="H18" s="42"/>
-      <c r="I18" s="56" t="s">
-        <v>111</v>
-      </c>
-      <c r="J18" s="64"/>
-      <c r="K18" s="43"/>
-      <c r="L18" s="109" t="s">
+      <c r="H18" s="41"/>
+      <c r="I18" s="55" t="s">
+        <v>98</v>
+      </c>
+      <c r="J18" s="63"/>
+      <c r="K18" s="42"/>
+      <c r="L18" s="108" t="s">
         <v>6</v>
       </c>
-      <c r="M18" s="58" t="s">
-        <v>129</v>
-      </c>
-      <c r="P18" s="55" t="s">
-        <v>71</v>
-      </c>
-      <c r="Q18" s="75"/>
-      <c r="R18" s="46" t="s">
-        <v>133</v>
-      </c>
-      <c r="S18" s="80"/>
-      <c r="T18" s="57" t="s">
-        <v>71</v>
+      <c r="M18" s="57" t="s">
+        <v>116</v>
+      </c>
+      <c r="P18" s="54" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q18" s="74"/>
+      <c r="R18" s="45" t="s">
+        <v>120</v>
+      </c>
+      <c r="S18" s="79"/>
+      <c r="T18" s="56" t="s">
+        <v>58</v>
       </c>
       <c r="U18" s="1" t="s">
-        <v>191</v>
+        <v>170</v>
       </c>
     </row>
     <row r="19" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2593,40 +2564,38 @@
       <c r="C19" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="D19" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="E19" s="25" t="s">
-        <v>65</v>
+      <c r="D19" s="8"/>
+      <c r="E19" s="22" t="s">
+        <v>54</v>
       </c>
       <c r="F19" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="H19" s="42" t="s">
-        <v>144</v>
-      </c>
-      <c r="I19" s="56" t="s">
-        <v>112</v>
-      </c>
-      <c r="J19" s="105" t="s">
-        <v>62</v>
-      </c>
-      <c r="K19" s="43"/>
-      <c r="L19" s="63"/>
-      <c r="M19" s="57" t="s">
-        <v>71</v>
-      </c>
-      <c r="P19" s="55" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q19" s="81"/>
-      <c r="R19" s="71"/>
-      <c r="S19" s="82"/>
-      <c r="T19" s="57" t="s">
+        <v>30</v>
+      </c>
+      <c r="H19" s="41" t="s">
         <v>131</v>
       </c>
+      <c r="I19" s="55" t="s">
+        <v>99</v>
+      </c>
+      <c r="J19" s="104" t="s">
+        <v>51</v>
+      </c>
+      <c r="K19" s="42"/>
+      <c r="L19" s="62"/>
+      <c r="M19" s="56" t="s">
+        <v>58</v>
+      </c>
+      <c r="P19" s="54" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q19" s="80"/>
+      <c r="R19" s="70"/>
+      <c r="S19" s="81"/>
+      <c r="T19" s="56" t="s">
+        <v>118</v>
+      </c>
       <c r="U19" s="1" t="s">
-        <v>185</v>
+        <v>166</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
@@ -2639,28 +2608,26 @@
       <c r="C20" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="D20" s="8" t="s">
-        <v>61</v>
-      </c>
+      <c r="D20" s="8"/>
       <c r="E20" s="17" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="H20" s="42" t="s">
-        <v>145</v>
-      </c>
-      <c r="I20" s="56" t="s">
-        <v>113</v>
-      </c>
-      <c r="J20" s="69" t="s">
-        <v>65</v>
-      </c>
-      <c r="K20" s="43"/>
-      <c r="L20" s="63"/>
-      <c r="M20" s="57" t="s">
-        <v>130</v>
+        <v>56</v>
+      </c>
+      <c r="H20" s="41" t="s">
+        <v>132</v>
+      </c>
+      <c r="I20" s="55" t="s">
+        <v>100</v>
+      </c>
+      <c r="J20" s="68" t="s">
+        <v>54</v>
+      </c>
+      <c r="K20" s="42"/>
+      <c r="L20" s="62"/>
+      <c r="M20" s="56" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
@@ -2674,25 +2641,23 @@
         <v>0</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="E21" s="22" t="s">
-        <v>24</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="E21" s="17"/>
       <c r="F21" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="H21" s="42"/>
-      <c r="I21" s="56" t="s">
-        <v>114</v>
-      </c>
-      <c r="J21" s="64"/>
-      <c r="K21" s="46" t="s">
-        <v>133</v>
-      </c>
-      <c r="L21" s="63"/>
-      <c r="M21" s="57" t="s">
-        <v>131</v>
+      <c r="H21" s="41"/>
+      <c r="I21" s="55" t="s">
+        <v>101</v>
+      </c>
+      <c r="J21" s="63"/>
+      <c r="K21" s="45" t="s">
+        <v>120</v>
+      </c>
+      <c r="L21" s="62"/>
+      <c r="M21" s="56" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="22" spans="1:21" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2705,24 +2670,26 @@
       <c r="C22" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="D22" s="8"/>
+      <c r="D22" s="8" t="s">
+        <v>193</v>
+      </c>
       <c r="E22" s="17"/>
       <c r="F22" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="H22" s="42"/>
-      <c r="I22" s="55" t="s">
-        <v>115</v>
-      </c>
-      <c r="J22" s="70"/>
-      <c r="K22" s="71"/>
-      <c r="L22" s="72"/>
-      <c r="M22" s="57" t="s">
-        <v>132</v>
+      <c r="H22" s="41"/>
+      <c r="I22" s="54" t="s">
+        <v>102</v>
+      </c>
+      <c r="J22" s="69"/>
+      <c r="K22" s="70"/>
+      <c r="L22" s="71"/>
+      <c r="M22" s="56" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A23" s="38">
+      <c r="A23" s="37">
         <v>21</v>
       </c>
       <c r="B23" s="10" t="s">
@@ -2737,11 +2704,11 @@
         <v>13</v>
       </c>
       <c r="P23" s="3" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A24" s="38">
+      <c r="A24" s="37">
         <v>22</v>
       </c>
       <c r="B24" s="10" t="s">
@@ -2751,24 +2718,23 @@
         <v>0</v>
       </c>
       <c r="D24" s="8"/>
-      <c r="E24" s="17"/>
       <c r="F24" s="15" t="s">
         <v>14</v>
       </c>
       <c r="P24" s="3" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="Q24" s="3" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="R24" s="3" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="S24" s="3" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="T24" s="3" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
@@ -2782,11 +2748,9 @@
         <v>0</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="E25" s="22" t="s">
-        <v>26</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="E25" s="17"/>
       <c r="F25" s="14" t="s">
         <v>15</v>
       </c>
@@ -2794,16 +2758,16 @@
         <v>1</v>
       </c>
       <c r="Q25" s="19" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="R25" s="19">
         <v>17</v>
       </c>
-      <c r="S25" s="32" t="s">
-        <v>83</v>
+      <c r="S25" s="31" t="s">
+        <v>70</v>
       </c>
       <c r="T25" s="19" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
@@ -2816,11 +2780,9 @@
       <c r="C26" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="D26" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="E26" s="23" t="s">
-        <v>68</v>
+      <c r="D26" s="8"/>
+      <c r="E26" s="22" t="s">
+        <v>57</v>
       </c>
       <c r="F26" s="8"/>
       <c r="I26" s="2" t="s">
@@ -2829,19 +2791,19 @@
       <c r="P26" s="17">
         <v>2</v>
       </c>
-      <c r="Q26" s="44" t="s">
-        <v>63</v>
-      </c>
-      <c r="R26" s="29">
+      <c r="Q26" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="R26" s="28">
         <v>5</v>
       </c>
-      <c r="S26" s="45" t="s">
-        <v>84</v>
-      </c>
-      <c r="T26" s="29" t="s">
-        <v>92</v>
-      </c>
-      <c r="U26" s="31"/>
+      <c r="S26" s="44" t="s">
+        <v>71</v>
+      </c>
+      <c r="T26" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="U26" s="30"/>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
@@ -2860,16 +2822,16 @@
         <v>3</v>
       </c>
       <c r="Q27" s="19" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="R27" s="19">
         <v>13</v>
       </c>
-      <c r="S27" s="32" t="s">
-        <v>85</v>
+      <c r="S27" s="31" t="s">
+        <v>72</v>
       </c>
       <c r="T27" s="19" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
@@ -2889,16 +2851,16 @@
         <v>4</v>
       </c>
       <c r="Q28" s="17" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="R28" s="17">
         <v>16</v>
       </c>
       <c r="S28" s="5" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="T28" s="17" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
@@ -2911,23 +2873,25 @@
       <c r="C29" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="D29" s="8"/>
+      <c r="D29" s="8" t="s">
+        <v>187</v>
+      </c>
       <c r="E29" s="17"/>
       <c r="F29" s="8"/>
       <c r="P29" s="19">
         <v>5</v>
       </c>
       <c r="Q29" s="19" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="R29" s="19">
         <v>14</v>
       </c>
-      <c r="S29" s="32" t="s">
-        <v>87</v>
+      <c r="S29" s="31" t="s">
+        <v>74</v>
       </c>
       <c r="T29" s="19" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
@@ -2946,13 +2910,13 @@
       <c r="P30" s="17">
         <v>6</v>
       </c>
-      <c r="Q30" s="29"/>
-      <c r="R30" s="29"/>
+      <c r="Q30" s="28"/>
+      <c r="R30" s="28"/>
       <c r="S30" s="5" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="T30" s="17" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
@@ -2966,8 +2930,8 @@
         <v>6</v>
       </c>
       <c r="D31" s="8"/>
-      <c r="E31" s="25" t="s">
-        <v>57</v>
+      <c r="E31" s="24" t="s">
+        <v>47</v>
       </c>
       <c r="F31" s="8" t="s">
         <v>8</v>
@@ -2976,18 +2940,18 @@
         <v>0</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="P31" s="19">
         <v>7</v>
       </c>
       <c r="Q31" s="19"/>
       <c r="R31" s="19"/>
-      <c r="S31" s="32" t="s">
-        <v>89</v>
+      <c r="S31" s="31" t="s">
+        <v>76</v>
       </c>
       <c r="T31" s="19" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
@@ -3000,10 +2964,8 @@
       <c r="C32" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="D32" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="E32" s="26" t="s">
+      <c r="D32" s="8"/>
+      <c r="E32" s="25" t="s">
         <v>23</v>
       </c>
       <c r="F32" s="8" t="s">
@@ -3013,7 +2975,7 @@
         <v>0</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="P32" s="17">
         <v>8</v>
@@ -3021,13 +2983,13 @@
       <c r="Q32" s="17"/>
       <c r="R32" s="17"/>
       <c r="S32" s="5" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="T32" s="17" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
         <v>36</v>
       </c>
@@ -3037,10 +2999,8 @@
       <c r="C33" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="D33" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="E33" s="25"/>
+      <c r="D33" s="8"/>
+      <c r="E33" s="24"/>
       <c r="F33" s="8" t="s">
         <v>8</v>
       </c>
@@ -3048,21 +3008,21 @@
         <v>0</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="P33" s="28">
+        <v>34</v>
+      </c>
+      <c r="P33" s="27">
         <v>9</v>
       </c>
-      <c r="Q33" s="28" t="s">
-        <v>73</v>
-      </c>
-      <c r="R33" s="28" t="s">
-        <v>73</v>
-      </c>
-      <c r="S33" s="36"/>
-      <c r="T33" s="36"/>
-    </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="Q33" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="R33" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="S33" s="35"/>
+      <c r="T33" s="35"/>
+    </row>
+    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
         <v>39</v>
       </c>
@@ -3073,8 +3033,8 @@
         <v>6</v>
       </c>
       <c r="D34" s="8"/>
-      <c r="E34" s="25" t="s">
-        <v>58</v>
+      <c r="E34" s="24" t="s">
+        <v>48</v>
       </c>
       <c r="F34" s="8" t="s">
         <v>8</v>
@@ -3083,422 +3043,492 @@
         <v>6</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="P34" s="29">
+        <v>33</v>
+      </c>
+      <c r="P34" s="28">
         <v>10</v>
       </c>
-      <c r="Q34" s="29" t="s">
-        <v>71</v>
-      </c>
-      <c r="R34" s="29" t="s">
-        <v>71</v>
-      </c>
-      <c r="S34" s="37"/>
-      <c r="T34" s="37"/>
-    </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="Q34" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="R34" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="S34" s="36"/>
+      <c r="T34" s="36"/>
+    </row>
+    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="37" spans="1:20" ht="18.75" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I37" s="54" t="s">
-        <v>172</v>
-      </c>
-      <c r="P37" s="54" t="s">
-        <v>200</v>
-      </c>
-      <c r="Q37" s="54"/>
-      <c r="R37" s="111" t="s">
+        <v>39</v>
+      </c>
+      <c r="I37" s="53" t="s">
+        <v>153</v>
+      </c>
+      <c r="P37" s="53" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="Q37" s="53"/>
+      <c r="R37" s="53" t="s">
+        <v>182</v>
+      </c>
+      <c r="T37" s="110" t="s">
+        <v>160</v>
+      </c>
+      <c r="U37" s="53" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="19">
         <v>1</v>
       </c>
       <c r="B38" s="19" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="C38" s="19">
         <v>4</v>
       </c>
-      <c r="D38" s="32" t="s">
-        <v>83</v>
+      <c r="D38" s="31" t="s">
+        <v>70</v>
       </c>
       <c r="E38" s="19" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="P38" s="19">
         <v>1</v>
       </c>
       <c r="Q38" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="R38" s="35" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="39" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>58</v>
+      </c>
+      <c r="R38" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="S38" s="27"/>
+      <c r="T38" s="34" t="s">
+        <v>173</v>
+      </c>
+      <c r="U38" s="27" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="17">
         <v>2</v>
       </c>
-      <c r="B39" s="44" t="s">
-        <v>63</v>
-      </c>
-      <c r="C39" s="29">
+      <c r="B39" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="C39" s="28">
         <v>5</v>
       </c>
-      <c r="D39" s="45" t="s">
-        <v>84</v>
-      </c>
-      <c r="E39" s="29" t="s">
-        <v>92</v>
-      </c>
-      <c r="F39" s="31" t="s">
-        <v>101</v>
-      </c>
-      <c r="H39" s="42" t="s">
-        <v>137</v>
-      </c>
-      <c r="I39" s="47" t="s">
+      <c r="D39" s="44" t="s">
+        <v>71</v>
+      </c>
+      <c r="E39" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="F39" s="30" t="s">
+        <v>88</v>
+      </c>
+      <c r="H39" s="41" t="s">
+        <v>124</v>
+      </c>
+      <c r="I39" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="M39" s="37" t="s">
+      <c r="M39" s="36" t="s">
         <v>9</v>
       </c>
       <c r="N39" s="1" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="P39" s="17">
         <v>2</v>
       </c>
       <c r="Q39" s="17" t="s">
-        <v>192</v>
-      </c>
-      <c r="R39" s="34" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
+        <v>171</v>
+      </c>
+      <c r="R39" s="17" t="s">
+        <v>171</v>
+      </c>
+      <c r="S39" s="28"/>
+      <c r="T39" s="33" t="s">
+        <v>172</v>
+      </c>
+      <c r="U39" s="28" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="19">
         <v>3</v>
       </c>
       <c r="B40" s="19" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="C40" s="19">
         <v>13</v>
       </c>
-      <c r="D40" s="32" t="s">
-        <v>85</v>
+      <c r="D40" s="31" t="s">
+        <v>72</v>
       </c>
       <c r="E40" s="19" t="s">
-        <v>93</v>
-      </c>
-      <c r="I40" s="55" t="s">
-        <v>178</v>
-      </c>
-      <c r="J40" s="73"/>
-      <c r="K40" s="88" t="s">
-        <v>174</v>
-      </c>
-      <c r="L40" s="83"/>
-      <c r="M40" s="57" t="s">
-        <v>131</v>
+        <v>80</v>
+      </c>
+      <c r="I40" s="54" t="s">
+        <v>159</v>
+      </c>
+      <c r="J40" s="72"/>
+      <c r="K40" s="87" t="s">
+        <v>155</v>
+      </c>
+      <c r="L40" s="82"/>
+      <c r="M40" s="56" t="s">
+        <v>118</v>
       </c>
       <c r="P40" s="19">
         <v>3</v>
       </c>
       <c r="Q40" s="19" t="s">
-        <v>193</v>
-      </c>
-      <c r="R40" s="35" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
+        <v>172</v>
+      </c>
+      <c r="R40" s="27" t="s">
+        <v>92</v>
+      </c>
+      <c r="S40" s="27"/>
+      <c r="T40" s="34" t="s">
+        <v>174</v>
+      </c>
+      <c r="U40" s="27" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="17">
         <v>4</v>
       </c>
       <c r="B41" s="17" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="C41" s="17">
         <v>16</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="E41" s="17" t="s">
-        <v>94</v>
-      </c>
-      <c r="I41" s="55" t="s">
-        <v>71</v>
-      </c>
-      <c r="J41" s="75"/>
-      <c r="K41" s="89"/>
-      <c r="L41" s="98" t="s">
-        <v>0</v>
-      </c>
-      <c r="M41" s="58" t="s">
-        <v>113</v>
+        <v>81</v>
+      </c>
+      <c r="I41" s="54" t="s">
+        <v>58</v>
+      </c>
+      <c r="J41" s="74"/>
+      <c r="K41" s="88"/>
+      <c r="L41" s="97" t="s">
+        <v>0</v>
+      </c>
+      <c r="M41" s="57" t="s">
+        <v>100</v>
       </c>
       <c r="P41" s="17">
         <v>4</v>
       </c>
       <c r="Q41" s="17" t="s">
-        <v>194</v>
-      </c>
-      <c r="R41" s="34" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
+        <v>173</v>
+      </c>
+      <c r="R41" s="28" t="s">
+        <v>93</v>
+      </c>
+      <c r="S41" s="28"/>
+      <c r="T41" s="33" t="s">
+        <v>102</v>
+      </c>
+      <c r="U41" s="28" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="19">
         <v>5</v>
       </c>
       <c r="B42" s="19" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C42" s="19">
         <v>14</v>
       </c>
-      <c r="D42" s="32" t="s">
-        <v>87</v>
+      <c r="D42" s="31" t="s">
+        <v>74</v>
       </c>
       <c r="E42" s="19" t="s">
-        <v>95</v>
-      </c>
-      <c r="I42" s="56" t="s">
-        <v>111</v>
-      </c>
-      <c r="J42" s="99" t="s">
-        <v>0</v>
-      </c>
-      <c r="K42" s="43"/>
-      <c r="L42" s="100" t="s">
-        <v>136</v>
-      </c>
-      <c r="M42" s="58" t="s">
-        <v>103</v>
+        <v>82</v>
+      </c>
+      <c r="I42" s="55" t="s">
+        <v>98</v>
+      </c>
+      <c r="J42" s="98" t="s">
+        <v>0</v>
+      </c>
+      <c r="K42" s="42"/>
+      <c r="L42" s="99" t="s">
+        <v>123</v>
+      </c>
+      <c r="M42" s="57" t="s">
+        <v>90</v>
       </c>
       <c r="P42" s="19">
         <v>5</v>
       </c>
       <c r="Q42" s="19" t="s">
-        <v>115</v>
-      </c>
-      <c r="R42" s="35" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+      <c r="R42" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="S42" s="27"/>
+      <c r="T42" s="34" t="s">
+        <v>175</v>
+      </c>
+      <c r="U42" s="27" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="17">
         <v>6</v>
       </c>
-      <c r="B43" s="29"/>
-      <c r="C43" s="29"/>
+      <c r="B43" s="28"/>
+      <c r="C43" s="28"/>
       <c r="D43" s="5" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="E43" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="I43" s="56" t="s">
-        <v>123</v>
-      </c>
-      <c r="J43" s="101" t="s">
-        <v>0</v>
-      </c>
-      <c r="K43" s="43"/>
-      <c r="L43" s="84"/>
-      <c r="M43" s="57" t="s">
-        <v>71</v>
+        <v>83</v>
+      </c>
+      <c r="I43" s="55" t="s">
+        <v>110</v>
+      </c>
+      <c r="J43" s="100" t="s">
+        <v>0</v>
+      </c>
+      <c r="K43" s="42"/>
+      <c r="L43" s="83"/>
+      <c r="M43" s="56" t="s">
+        <v>58</v>
       </c>
       <c r="P43" s="17">
         <v>6</v>
       </c>
       <c r="Q43" s="17" t="s">
-        <v>195</v>
-      </c>
-      <c r="R43" s="34" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
+        <v>174</v>
+      </c>
+      <c r="R43" s="112" t="s">
+        <v>112</v>
+      </c>
+      <c r="S43" s="112"/>
+      <c r="T43" s="33" t="s">
+        <v>176</v>
+      </c>
+      <c r="U43" s="112" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="19">
         <v>7</v>
       </c>
       <c r="B44" s="19"/>
       <c r="C44" s="19"/>
-      <c r="D44" s="32" t="s">
-        <v>89</v>
+      <c r="D44" s="31" t="s">
+        <v>76</v>
       </c>
       <c r="E44" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="I44" s="56" t="s">
-        <v>104</v>
-      </c>
-      <c r="J44" s="101" t="s">
-        <v>0</v>
-      </c>
-      <c r="K44" s="43"/>
-      <c r="L44" s="84"/>
-      <c r="M44" s="57" t="s">
-        <v>177</v>
+        <v>84</v>
+      </c>
+      <c r="I44" s="55" t="s">
+        <v>91</v>
+      </c>
+      <c r="J44" s="100" t="s">
+        <v>0</v>
+      </c>
+      <c r="K44" s="42"/>
+      <c r="L44" s="83"/>
+      <c r="M44" s="56" t="s">
+        <v>158</v>
       </c>
       <c r="P44" s="19">
         <v>7</v>
       </c>
       <c r="Q44" s="19" t="s">
-        <v>196</v>
-      </c>
-      <c r="R44" s="35" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
+        <v>175</v>
+      </c>
+      <c r="R44" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="S44" s="27"/>
+      <c r="T44" s="34" t="s">
+        <v>171</v>
+      </c>
+      <c r="U44" s="27" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="17">
         <v>8</v>
       </c>
       <c r="B45" s="17"/>
       <c r="C45" s="17"/>
       <c r="D45" s="5" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="E45" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="I45" s="56" t="s">
-        <v>110</v>
-      </c>
-      <c r="J45" s="101" t="s">
-        <v>0</v>
-      </c>
-      <c r="K45" s="43"/>
-      <c r="L45" s="93" t="s">
-        <v>134</v>
-      </c>
-      <c r="M45" s="58" t="s">
-        <v>116</v>
+        <v>85</v>
+      </c>
+      <c r="I45" s="55" t="s">
+        <v>97</v>
+      </c>
+      <c r="J45" s="100" t="s">
+        <v>0</v>
+      </c>
+      <c r="K45" s="42"/>
+      <c r="L45" s="92" t="s">
+        <v>121</v>
+      </c>
+      <c r="M45" s="57" t="s">
+        <v>103</v>
       </c>
       <c r="P45" s="17">
         <v>8</v>
       </c>
-      <c r="Q45" s="112" t="s">
-        <v>201</v>
-      </c>
-      <c r="R45" s="34" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A46" s="28">
+      <c r="Q45" s="111" t="s">
+        <v>180</v>
+      </c>
+      <c r="R45" s="28"/>
+      <c r="S45" s="28"/>
+      <c r="T45" s="33" t="s">
+        <v>177</v>
+      </c>
+      <c r="U45" s="28" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="46" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A46" s="27">
         <v>9</v>
       </c>
-      <c r="B46" s="28" t="s">
-        <v>73</v>
-      </c>
-      <c r="C46" s="28" t="s">
-        <v>73</v>
-      </c>
-      <c r="D46" s="36"/>
-      <c r="E46" s="36"/>
-      <c r="I46" s="56" t="s">
-        <v>125</v>
-      </c>
-      <c r="J46" s="99" t="s">
-        <v>0</v>
-      </c>
-      <c r="K46" s="43"/>
-      <c r="L46" s="93" t="s">
-        <v>135</v>
-      </c>
-      <c r="M46" s="58" t="s">
-        <v>117</v>
-      </c>
-      <c r="P46" s="28">
+      <c r="B46" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="C46" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="D46" s="35"/>
+      <c r="E46" s="35"/>
+      <c r="I46" s="55" t="s">
+        <v>112</v>
+      </c>
+      <c r="J46" s="98" t="s">
+        <v>0</v>
+      </c>
+      <c r="K46" s="42"/>
+      <c r="L46" s="92" t="s">
+        <v>122</v>
+      </c>
+      <c r="M46" s="57" t="s">
+        <v>104</v>
+      </c>
+      <c r="P46" s="27">
         <v>9</v>
       </c>
-      <c r="R46" s="35" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="47" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="29">
+      <c r="R46" s="27"/>
+      <c r="S46" s="27"/>
+      <c r="T46" s="34" t="s">
+        <v>178</v>
+      </c>
+      <c r="U46" s="27" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="47" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="28">
         <v>10</v>
       </c>
-      <c r="B47" s="29" t="s">
-        <v>71</v>
-      </c>
-      <c r="C47" s="29" t="s">
-        <v>71</v>
-      </c>
-      <c r="D47" s="37"/>
-      <c r="E47" s="37"/>
-      <c r="I47" s="56" t="s">
-        <v>112</v>
-      </c>
-      <c r="J47" s="102" t="s">
-        <v>0</v>
-      </c>
-      <c r="K47" s="85"/>
-      <c r="L47" s="94"/>
-      <c r="M47" s="57" t="s">
-        <v>71</v>
-      </c>
-      <c r="P47" s="29">
+      <c r="B47" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="C47" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="D47" s="36"/>
+      <c r="E47" s="36"/>
+      <c r="I47" s="55" t="s">
+        <v>99</v>
+      </c>
+      <c r="J47" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="K47" s="84"/>
+      <c r="L47" s="93"/>
+      <c r="M47" s="56" t="s">
+        <v>58</v>
+      </c>
+      <c r="P47" s="28">
         <v>10</v>
       </c>
-      <c r="R47" s="34" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="J48" s="95"/>
-      <c r="K48" s="96" t="s">
-        <v>173</v>
-      </c>
-      <c r="L48" s="97"/>
+      <c r="R47" s="28"/>
+      <c r="S47" s="28"/>
+      <c r="T47" s="33" t="s">
+        <v>58</v>
+      </c>
+      <c r="U47" s="28" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="J48" s="94"/>
+      <c r="K48" s="95" t="s">
+        <v>154</v>
+      </c>
+      <c r="L48" s="96"/>
     </row>
     <row r="49" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="J49" s="90"/>
-      <c r="K49" s="91"/>
-      <c r="L49" s="92"/>
+        <v>68</v>
+      </c>
+      <c r="J49" s="89"/>
+      <c r="K49" s="90"/>
+      <c r="L49" s="91"/>
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D50" s="41" t="s">
-        <v>80</v>
+        <v>38</v>
+      </c>
+      <c r="D50" s="40" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.25">
@@ -3506,12 +3536,12 @@
         <v>1</v>
       </c>
       <c r="B51" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="C51" s="28">
+        <v>47</v>
+      </c>
+      <c r="C51" s="27">
         <v>34</v>
       </c>
-      <c r="D51" s="39">
+      <c r="D51" s="38">
         <v>34</v>
       </c>
     </row>
@@ -3519,13 +3549,13 @@
       <c r="A52" s="17">
         <v>2</v>
       </c>
-      <c r="B52" s="33" t="s">
-        <v>74</v>
-      </c>
-      <c r="C52" s="29">
+      <c r="B52" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="C52" s="28">
         <v>39</v>
       </c>
-      <c r="D52" s="40">
+      <c r="D52" s="39">
         <v>39</v>
       </c>
     </row>
@@ -3534,36 +3564,36 @@
         <v>3</v>
       </c>
       <c r="B53" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="C53" s="28">
+        <v>62</v>
+      </c>
+      <c r="C53" s="27">
         <v>2</v>
       </c>
-      <c r="D53" s="39"/>
+      <c r="D53" s="38"/>
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A54" s="17">
         <v>4</v>
       </c>
       <c r="B54" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="C54" s="29">
+        <v>63</v>
+      </c>
+      <c r="C54" s="28">
         <v>33</v>
       </c>
-      <c r="D54" s="40"/>
+      <c r="D54" s="39"/>
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A55" s="19">
         <v>5</v>
       </c>
       <c r="B55" s="19" t="s">
-        <v>77</v>
-      </c>
-      <c r="C55" s="28">
+        <v>64</v>
+      </c>
+      <c r="C55" s="27">
         <v>21</v>
       </c>
-      <c r="D55" s="39">
+      <c r="D55" s="38">
         <v>21</v>
       </c>
     </row>
@@ -3571,13 +3601,13 @@
       <c r="A56" s="17">
         <v>6</v>
       </c>
-      <c r="B56" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="C56" s="29">
+      <c r="B56" s="28" t="s">
+        <v>65</v>
+      </c>
+      <c r="C56" s="28">
         <v>22</v>
       </c>
-      <c r="D56" s="40">
+      <c r="D56" s="39">
         <v>22</v>
       </c>
     </row>
@@ -3585,75 +3615,75 @@
       <c r="A57" s="19">
         <v>7</v>
       </c>
-      <c r="B57" s="28" t="s">
-        <v>71</v>
-      </c>
-      <c r="C57" s="28" t="s">
-        <v>71</v>
-      </c>
-      <c r="D57" s="39" t="s">
-        <v>71</v>
+      <c r="B57" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="C57" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="D57" s="38" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A58" s="17">
         <v>8</v>
       </c>
-      <c r="B58" s="29" t="s">
-        <v>73</v>
-      </c>
-      <c r="C58" s="29" t="s">
-        <v>79</v>
-      </c>
-      <c r="D58" s="40" t="s">
-        <v>79</v>
+      <c r="B58" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="C58" s="28" t="s">
+        <v>66</v>
+      </c>
+      <c r="D58" s="39" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A59" s="28">
+      <c r="A59" s="27">
         <v>9</v>
       </c>
-      <c r="B59" s="28" t="s">
-        <v>71</v>
-      </c>
-      <c r="C59" s="28" t="s">
-        <v>71</v>
-      </c>
-      <c r="D59" s="39" t="s">
-        <v>71</v>
+      <c r="B59" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="C59" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="D59" s="38" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A60" s="29">
+      <c r="A60" s="28">
         <v>10</v>
       </c>
-      <c r="B60" s="29" t="s">
-        <v>73</v>
-      </c>
-      <c r="C60" s="29" t="s">
-        <v>79</v>
-      </c>
-      <c r="D60" s="40" t="s">
-        <v>79</v>
+      <c r="B60" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="C60" s="28" t="s">
+        <v>66</v>
+      </c>
+      <c r="D60" s="39" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C63" s="41" t="s">
-        <v>80</v>
+        <v>37</v>
+      </c>
+      <c r="C63" s="40" t="s">
+        <v>67</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.25">
@@ -3661,187 +3691,187 @@
         <v>1</v>
       </c>
       <c r="B64" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="C64" s="39">
+        <v>51</v>
+      </c>
+      <c r="C64" s="38">
         <v>4</v>
       </c>
-      <c r="D64" s="32" t="s">
-        <v>29</v>
+      <c r="D64" s="31" t="s">
+        <v>28</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="J64" s="48" t="s">
-        <v>155</v>
-      </c>
-      <c r="K64" s="48"/>
-      <c r="Q64" s="48"/>
-      <c r="R64" s="48"/>
+        <v>136</v>
+      </c>
+      <c r="J64" s="47" t="s">
+        <v>142</v>
+      </c>
+      <c r="K64" s="47"/>
+      <c r="Q64" s="47"/>
+      <c r="R64" s="47"/>
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A65" s="17">
         <v>2</v>
       </c>
-      <c r="B65" s="33" t="s">
-        <v>63</v>
-      </c>
-      <c r="C65" s="40">
+      <c r="B65" s="32" t="s">
+        <v>52</v>
+      </c>
+      <c r="C65" s="39">
         <v>5</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="L65" s="49" t="s">
-        <v>154</v>
-      </c>
-      <c r="M65" s="49"/>
-      <c r="N65" s="49"/>
+        <v>137</v>
+      </c>
+      <c r="L65" s="48" t="s">
+        <v>141</v>
+      </c>
+      <c r="M65" s="48"/>
+      <c r="N65" s="48"/>
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A66" s="19">
         <v>3</v>
       </c>
       <c r="B66" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="C66" s="39">
+        <v>53</v>
+      </c>
+      <c r="C66" s="38">
         <v>13</v>
       </c>
-      <c r="D66" s="32" t="s">
-        <v>50</v>
+      <c r="D66" s="31" t="s">
+        <v>40</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="M66" s="50"/>
-      <c r="N66" s="50"/>
+        <v>138</v>
+      </c>
+      <c r="M66" s="49"/>
+      <c r="N66" s="49"/>
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A67" s="17">
         <v>4</v>
       </c>
       <c r="B67" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="C67" s="40">
+        <v>54</v>
+      </c>
+      <c r="C67" s="39">
         <v>16</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="O67" s="51" t="s">
-        <v>156</v>
-      </c>
-      <c r="P67" s="51"/>
+        <v>139</v>
+      </c>
+      <c r="O67" s="50" t="s">
+        <v>143</v>
+      </c>
+      <c r="P67" s="50"/>
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A68" s="19">
         <v>5</v>
       </c>
       <c r="B68" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="C68" s="39">
+        <v>55</v>
+      </c>
+      <c r="C68" s="38">
         <v>14</v>
       </c>
-      <c r="D68" s="32" t="s">
-        <v>52</v>
+      <c r="D68" s="31" t="s">
+        <v>42</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="O68" s="52" t="s">
-        <v>157</v>
-      </c>
-      <c r="P68" s="52"/>
+        <v>140</v>
+      </c>
+      <c r="O68" s="51" t="s">
+        <v>144</v>
+      </c>
+      <c r="P68" s="51"/>
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A69" s="17">
         <v>6</v>
       </c>
-      <c r="B69" s="34" t="s">
+      <c r="B69" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="C69" s="34">
+      <c r="C69" s="33">
         <v>15</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="F69" s="31" t="s">
-        <v>72</v>
+        <v>43</v>
+      </c>
+      <c r="F69" s="30" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="70" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A70" s="19">
         <v>7</v>
       </c>
-      <c r="B70" s="35" t="s">
+      <c r="B70" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="C70" s="35">
+      <c r="C70" s="34">
         <v>18</v>
       </c>
-      <c r="D70" s="32" t="s">
-        <v>54</v>
-      </c>
-      <c r="F70" s="31" t="s">
-        <v>72</v>
+      <c r="D70" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="F70" s="30" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A71" s="17">
         <v>8</v>
       </c>
-      <c r="B71" s="34" t="s">
+      <c r="B71" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="C71" s="34">
+      <c r="C71" s="33">
         <v>23</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F71" s="31" t="s">
-        <v>72</v>
+        <v>45</v>
+      </c>
+      <c r="F71" s="30" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="72" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A72" s="28">
+      <c r="A72" s="27">
         <v>9</v>
       </c>
-      <c r="B72" s="35" t="s">
+      <c r="B72" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="C72" s="35">
+      <c r="C72" s="34">
         <v>35</v>
       </c>
-      <c r="D72" s="36" t="s">
-        <v>56</v>
-      </c>
-      <c r="F72" s="31" t="s">
-        <v>72</v>
+      <c r="D72" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="F72" s="30" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="73" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A73" s="29">
+      <c r="A73" s="28">
         <v>10</v>
       </c>
-      <c r="B73" s="30" t="s">
-        <v>60</v>
-      </c>
-      <c r="C73" s="40">
+      <c r="B73" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="C73" s="39">
         <v>17</v>
       </c>
-      <c r="D73" s="37" t="s">
-        <v>59</v>
+      <c r="D73" s="36" t="s">
+        <v>49</v>
       </c>
       <c r="G73" s="3"/>
     </row>

--- a/docs/ESP32 Pins.xlsx
+++ b/docs/ESP32 Pins.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="32160" windowHeight="15165"/>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="32160" windowHeight="15165"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="194">
   <si>
     <t>OK</t>
   </si>
@@ -1111,7 +1111,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="114">
+  <cellXfs count="115">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1451,6 +1451,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1461,6 +1464,7 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFFFF99"/>
       <color rgb="FFFF7D7D"/>
       <color rgb="FFF7AFDD"/>
       <color rgb="FFFBD5ED"/>
@@ -1917,7 +1921,7 @@
       <c r="C5" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="114" t="s">
         <v>191</v>
       </c>
       <c r="E5" s="5"/>
@@ -2520,7 +2524,7 @@
       <c r="C18" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D18" s="114" t="s">
         <v>185</v>
       </c>
       <c r="E18" s="113"/>
@@ -2609,9 +2613,7 @@
         <v>0</v>
       </c>
       <c r="D20" s="8"/>
-      <c r="E20" s="17" t="s">
-        <v>50</v>
-      </c>
+      <c r="E20" s="17"/>
       <c r="F20" s="8" t="s">
         <v>56</v>
       </c>
@@ -2640,7 +2642,7 @@
       <c r="C21" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="D21" s="114" t="s">
         <v>189</v>
       </c>
       <c r="E21" s="17"/>
@@ -2670,7 +2672,7 @@
       <c r="C22" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="D22" s="8" t="s">
+      <c r="D22" s="114" t="s">
         <v>193</v>
       </c>
       <c r="E22" s="17"/>
@@ -2747,7 +2749,7 @@
       <c r="C25" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="D25" s="8" t="s">
+      <c r="D25" s="114" t="s">
         <v>184</v>
       </c>
       <c r="E25" s="17"/>
@@ -2873,7 +2875,7 @@
       <c r="C29" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="D29" s="8" t="s">
+      <c r="D29" s="114" t="s">
         <v>187</v>
       </c>
       <c r="E29" s="17"/>
